--- a/questionnaire_templates/007_elder_care_access_insight_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/007_elder_care_access_insight_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Elder Care Services</t>
+          <t>Experiences with Elder Care Services</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,20 +548,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Barrier to Care Services</t>
+          <t>Barriers to Accessing Care Services</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Access to Care Services</t>
+          <t>Satisfaction with Care Services</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +589,18 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>satisfaction_with_services</t>
+          <t>regional_access_to_care_services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Satisfaction with Services</t>
+          <t>Regional Access to Care Services</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,87 +612,87 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>region_of_residence</t>
+          <t>demographic_characteristics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Region of Residence</t>
+          <t>Demographic Characteristics</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>regional_access_to_care_services</t>
+          <t>region_of_residence</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Regional Access to Care Services</t>
+          <t>Region of Residence</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>demographic_characteristics</t>
+          <t>region_served</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Demographic Characteristics</t>
+          <t>Region Served</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>care_services_satisfaction</t>
+          <t>care_services_benefits</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Care Services Satisfaction</t>
+          <t>Benefits of Care Services</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,18 +704,18 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>access_to_care_services</t>
+          <t>care_services_barriers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Access to Care Services</t>
+          <t>Care Services Barriers</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>region_served</t>
+          <t>satisfaction_with_services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Region Served</t>
+          <t>Satisfaction with Services</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>care_services_barriers</t>
+          <t>care_services_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Care Services Barriers</t>
+          <t>Care Services Satisfaction</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>care_services_benefits</t>
+          <t>regional_coverage</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Care Services Benefits</t>
+          <t>Regional Coverage</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -796,292 +796,131 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>care_services_satisfaction</t>
+          <t>care_services_access</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Care Services Satisfaction</t>
+          <t>Access to Care Services</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>elder_care_services</t>
+          <t>region_served_by_care_services</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Elder Care Services</t>
+          <t>Region Served by Care Services</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>region_of_residence</t>
+          <t>care_services_accessed</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Region of Residence</t>
+          <t>Care Services Access</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>satisfaction_with_services</t>
+          <t>elder_care_services_accessed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Satisfaction with Services</t>
+          <t>Elder Care Services Access</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>care_services_satisfaction</t>
+          <t>care_services_benefits_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Care Services Satisfaction</t>
+          <t>Care Services Benefits 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>care_services_satisfaction</t>
+          <t>elder_care_services_experience</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Care Services Satisfaction</t>
+          <t>Elder Care Services Experience</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>care_services_benefits</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Care Services Benefits</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>satisfaction_with_services</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Satisfaction with Services</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>care_services_satisfaction</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Care Services Satisfaction</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>care_services</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Care Services</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>care_services_satisfaction</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Care Services Satisfaction</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>region_served</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Region Served</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>regional_access_to_care_services</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Regional Access to Care Services</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C41"/>
+  <dimension ref="A1:C37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1126,41 +965,41 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>very dissatisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,68 +1016,68 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>very satisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>region_of_residence_choices</t>
+          <t>regional_access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_poor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>very poor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>region_of_residence_choices</t>
+          <t>regional_access_to_care_services_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>poor</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>very_poor</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>very poor</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>poor</t>
+          <t>good</t>
         </is>
       </c>
     </row>
@@ -1284,46 +1123,46 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>excellent</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>excellent</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>regional_access_to_care_services_choices</t>
+          <t>demographic_characteristics_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>male</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>regional_access_to_care_services_choices</t>
+          <t>demographic_characteristics_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>excellent</t>
+          <t>female</t>
         </is>
       </c>
     </row>
@@ -1335,199 +1174,199 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>demographic_characteristics_choices</t>
+          <t>region_served_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>region_served_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>care_services_benefits_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>access_to_care_services_choices</t>
+          <t>care_services_benefits_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>access_to_care_services_choices</t>
+          <t>care_services_barriers_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>region_served_choices</t>
+          <t>care_services_barriers_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>region_served_choices</t>
+          <t>satisfaction_with_services_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>care_services_barriers_choices</t>
+          <t>satisfaction_with_services_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>care_services_barriers_choices</t>
+          <t>care_services_satisfaction_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>care_services_benefits_choices</t>
+          <t>care_services_satisfaction_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>satisfied</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>care_services_benefits_choices</t>
+          <t>care_services_satisfaction_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>neutral</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1378,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1556,250 +1395,182 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>regional_coverage_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>regional_coverage_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>care_services_access_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>care_services_access_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>region_served_by_care_services_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>region_served_by_care_services_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>care_services_accessed_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>satisfaction_with_services_choices</t>
+          <t>care_services_accessed_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>elder_care_services_accessed_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>satisfied</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Satisfied</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>care_services_satisfaction_choices</t>
+          <t>elder_care_services_accessed_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dissatisfied</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dissatisfied</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>care_services_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>care_services_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>region_served_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>region_served_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
